--- a/shared/words/虚词大盘点.xlsx
+++ b/shared/words/虚词大盘点.xlsx
@@ -627,6 +627,11 @@
           <t>words/empty_words/doch.mp3</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lernst du nicht Deutsch? Doch!</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -649,6 +654,11 @@
           <t>words/empty_words/also.mp3</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Es regnet, also bleibe ich zu Hause.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,6 +681,11 @@
           <t>words/empty_words/dann.mp3</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dann verabschieden sie sich.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -693,6 +708,11 @@
           <t>words/empty_words/etwas.mp3</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hast du etwas Zeit?</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -715,6 +735,11 @@
           <t>words/empty_words/zwar.mp3</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist zwar jung, aber sehr erfahren.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -737,6 +762,11 @@
           <t>words/empty_words/auch.mp3</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich komme auch aus China.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -759,6 +789,11 @@
           <t>words/empty_words/noch.mp3</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie heißt das noch mal auf Deutsch?</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -781,6 +816,11 @@
           <t>words/empty_words/zu.mp3</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist zu teuer.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -803,6 +843,11 @@
           <t>words/empty_words/nur.mp3</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Lehrerin spricht im Unterricht nur Deutsch.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -825,6 +870,11 @@
           <t>words/empty_words/bloß.mp3</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was kann ich ihr bloß schenken?</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -982,6 +1032,11 @@
           <t>words/empty_words/gern.mp3</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich höre gern Musik.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1031,6 +1086,11 @@
           <t>words/empty_words/gleich.mp3</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich komme gleich.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1053,6 +1113,11 @@
           <t>words/empty_words/sofort.mp3</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er packt das Geschenk sofort aus.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1129,6 +1194,11 @@
           <t>words/empty_words/besonders.mp3</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Farbe steht mir nicht besonders.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1151,6 +1221,11 @@
           <t>words/empty_words/bestimmt.mp3</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das hier ist bestimmt deine Oma.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1173,6 +1248,11 @@
           <t>words/empty_words/sicher.mp3</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bist du sicher?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1195,6 +1275,11 @@
           <t>words/empty_words/vielleicht.mp3</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vielleicht kommt er morgen.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1244,6 +1329,11 @@
           <t>words/empty_words/hier.mp3</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hier sind zwei Pässe.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1293,6 +1383,11 @@
           <t>words/empty_words/da.mp3</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Da ist ein Taxi.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1315,6 +1410,11 @@
           <t>words/empty_words/sonst.mp3</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was wünschen Sie sonst noch?</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1337,6 +1437,11 @@
           <t>words/empty_words/eben.mp3</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist eben so.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1359,6 +1464,11 @@
           <t>words/empty_words/wieder.mp3</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist wieder krank.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1381,6 +1491,11 @@
           <t>words/empty_words/immer.mp3</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er kommt immer zu spät.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1457,6 +1572,11 @@
           <t>words/empty_words/oft.mp3</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sie fährt oft Fahrrad.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1506,6 +1626,11 @@
           <t>words/empty_words/so.mp3</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stehst du so früh auf?</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1528,6 +1653,11 @@
           <t>words/empty_words/übrigens.mp3</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Übrigens, mein Name ist Wang.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1604,6 +1734,11 @@
           <t>words/empty_words/als.mp3</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Als ich klein war, wohnte ich in Beijing.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1624,6 +1759,11 @@
       <c r="F48" t="inlineStr">
         <is>
           <t>words/empty_words/etwa.mp3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das dauert etwa zehn Minuten.</t>
         </is>
       </c>
     </row>
